--- a/deliverables/06_ผลการทดสอบ/Nestly-UI-Test-Report.xlsx
+++ b/deliverables/06_ผลการทดสอบ/Nestly-UI-Test-Report.xlsx
@@ -22,10 +22,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd hh:mm:ss"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -158,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -231,10 +232,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2062,7 +2060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H42"/>
+  <dimension ref="B2:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2097,7 +2095,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29 19:00 – 19:18 (4 รอบ ดูประวัติการรันด้านล่าง)</t>
+          <t>2026-10-29 19:50 – 19:54 (4 รอบ ดูประวัติการรันด้านล่าง)</t>
         </is>
       </c>
     </row>
@@ -2393,121 +2391,118 @@
     <row r="23">
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>ผลสุดท้าย (ใช้ผลรอบล่าสุดของแต่ละเคส)</t>
+          <t>รอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-29 19:18</t>
-        </is>
-      </c>
-      <c r="D23" s="10">
-        <f>C14</f>
-        <v/>
-      </c>
-      <c r="E23" s="10">
-        <f>D14</f>
-        <v/>
-      </c>
-      <c r="F23" s="10">
-        <f>E14</f>
-        <v/>
-      </c>
-      <c r="G23" s="10">
-        <f>F14</f>
-        <v/>
+          <t>2026-10-29 19:50</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="H23" s="11">
         <f>IF(D23=0,0,E23/D23)</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>รอบที่ 1 ไม่ผ่าน 11 เคส ส่วนใหญ่เป็น timeout ตอนเปิดหน้าครั้งแรก เพราะ next dev --webpack คอมไพล์หน้าช้า และมี 3 เคสที่ไม่ได้รัน (Untested ในรอบนั้น) · รอบที่ 2–4 รันซ้ำตอนที่ server คอมไพล์หน้าไว้แล้ว · เทียบกับ GitHub Actions CI run #107 บน commit 24a0107 เดียวกันที่ผ่านทุก job</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="7" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>ผลสุดท้าย (ใช้ผลรอบล่าสุดของแต่ละเคส)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-29 19:54</t>
+        </is>
+      </c>
+      <c r="D24" s="10">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="E24" s="10">
+        <f>D14</f>
+        <v/>
+      </c>
+      <c r="F24" s="10">
+        <f>E14</f>
+        <v/>
+      </c>
+      <c r="G24" s="10">
+        <f>F14</f>
+        <v/>
+      </c>
+      <c r="H24" s="11">
+        <f>IF(D24=0,0,E24/D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>รอบที่ 1–4 รันด้วย next dev --webpack (ช้ากว่าปกติ) รอบที่ 1 ไม่ผ่าน 11 เคส ส่วนใหญ่เป็น timeout ตอนเปิดหน้าครั้งแรก · รอบที่ 2–4 รันซ้ำเหลือไม่ผ่านซ้ำ 2 เคส วิเคราะห์แล้วเคสแชทเป็นบัคจริง (BUG-UI-001) แก้แล้ว · รอบที่ 5 รันทั้งชุดหลังแก้ ด้วย Turbopack และ retry 2 ครั้งแบบเดียวกับ GitHub Actions CI · ผลใน Test Cases ใช้ผลรอบล่าสุดของแต่ละเคส</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>แยกตามส่วนของระบบ / โมดูล</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="8" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>Module / Feature</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>ทั้งหมด</t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>Untested</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>อัตราผ่าน</t>
         </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Accessibility</t>
-        </is>
-      </c>
-      <c r="C28" s="10">
-        <f>COUNTIF('Test Cases'!$B$3:$B$300,$B28)</f>
-        <v/>
-      </c>
-      <c r="D28" s="10">
-        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B28,'Test Cases'!$I$3:$I$300,"Pass")</f>
-        <v/>
-      </c>
-      <c r="E28" s="10">
-        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B28,'Test Cases'!$I$3:$I$300,"Fail")</f>
-        <v/>
-      </c>
-      <c r="F28" s="10">
-        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B28,'Test Cases'!$I$3:$I$300,"Block")</f>
-        <v/>
-      </c>
-      <c r="G28" s="10">
-        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B28,'Test Cases'!$I$3:$I$300,"Untested")</f>
-        <v/>
-      </c>
-      <c r="H28" s="11">
-        <f>IF(C28-G28=0,0,D28/(C28-G28))</f>
-        <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Login</t>
+          <t>Accessibility</t>
         </is>
       </c>
       <c r="C29" s="10">
@@ -2538,7 +2533,7 @@
     <row r="30" ht="18" customHeight="1">
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Super Admin Dashboard</t>
+          <t>Login</t>
         </is>
       </c>
       <c r="C30" s="10">
@@ -2569,7 +2564,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Color Contrast (WCAG)</t>
+          <t>Super Admin Dashboard</t>
         </is>
       </c>
       <c r="C31" s="10">
@@ -2600,7 +2595,7 @@
     <row r="32" ht="18" customHeight="1">
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Billing Lifecycle</t>
+          <t>Color Contrast (WCAG)</t>
         </is>
       </c>
       <c r="C32" s="10">
@@ -2631,7 +2626,7 @@
     <row r="33" ht="18" customHeight="1">
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Keyboard Access</t>
+          <t>Billing Lifecycle</t>
         </is>
       </c>
       <c r="C33" s="10">
@@ -2662,7 +2657,7 @@
     <row r="34" ht="18" customHeight="1">
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Lease Renewal</t>
+          <t>Keyboard Access</t>
         </is>
       </c>
       <c r="C34" s="10">
@@ -2693,7 +2688,7 @@
     <row r="35" ht="18" customHeight="1">
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Mobile Touch Target</t>
+          <t>Lease Renewal</t>
         </is>
       </c>
       <c r="C35" s="10">
@@ -2724,7 +2719,7 @@
     <row r="36" ht="18" customHeight="1">
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Performance (Requests)</t>
+          <t>Mobile Touch Target</t>
         </is>
       </c>
       <c r="C36" s="10">
@@ -2755,7 +2750,7 @@
     <row r="37" ht="18" customHeight="1">
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Responsive</t>
+          <t>Performance (Requests)</t>
         </is>
       </c>
       <c r="C37" s="10">
@@ -2786,7 +2781,7 @@
     <row r="38" ht="18" customHeight="1">
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Subscription Access</t>
+          <t>Responsive</t>
         </is>
       </c>
       <c r="C38" s="10">
@@ -2817,7 +2812,7 @@
     <row r="39" ht="18" customHeight="1">
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Session Management</t>
+          <t>Subscription Access</t>
         </is>
       </c>
       <c r="C39" s="10">
@@ -2848,7 +2843,7 @@
     <row r="40" ht="18" customHeight="1">
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Table Contract</t>
+          <t>Session Management</t>
         </is>
       </c>
       <c r="C40" s="10">
@@ -2879,7 +2874,7 @@
     <row r="41" ht="18" customHeight="1">
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Owner Journey</t>
+          <t>Table Contract</t>
         </is>
       </c>
       <c r="C41" s="10">
@@ -2910,7 +2905,7 @@
     <row r="42" ht="18" customHeight="1">
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Tenant Journey</t>
+          <t>Owner Journey</t>
         </is>
       </c>
       <c r="C42" s="10">
@@ -2935,6 +2930,37 @@
       </c>
       <c r="H42" s="11">
         <f>IF(C42-G42=0,0,D42/(C42-G42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>Tenant Journey</t>
+        </is>
+      </c>
+      <c r="C43" s="10">
+        <f>COUNTIF('Test Cases'!$B$3:$B$300,$B43)</f>
+        <v/>
+      </c>
+      <c r="D43" s="10">
+        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B43,'Test Cases'!$I$3:$I$300,"Pass")</f>
+        <v/>
+      </c>
+      <c r="E43" s="10">
+        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B43,'Test Cases'!$I$3:$I$300,"Fail")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B43,'Test Cases'!$I$3:$I$300,"Block")</f>
+        <v/>
+      </c>
+      <c r="G43" s="10">
+        <f>COUNTIFS('Test Cases'!$B$3:$B$300,$B43,'Test Cases'!$I$3:$I$300,"Untested")</f>
+        <v/>
+      </c>
+      <c r="H43" s="11">
+        <f>IF(C43-G43=0,0,D43/(C43-G43))</f>
         <v/>
       </c>
     </row>
@@ -2943,11 +2969,11 @@
     <mergeCell ref="C6:H6"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="C9:H9"/>
-    <mergeCell ref="B24:H24"/>
     <mergeCell ref="C8:H8"/>
+    <mergeCell ref="B25:H25"/>
     <mergeCell ref="C7:H7"/>
   </mergeCells>
-  <conditionalFormatting sqref="H14:H43">
+  <conditionalFormatting sqref="H14:H44">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(ISNUMBER(H14),H14&lt;1)</formula>
     </cfRule>
@@ -3180,7 +3206,7 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="56" customHeight="1">
       <c r="B25" s="13" t="inlineStr">
         <is>
           <t>หมายเหตุรอบนี้</t>
@@ -3188,7 +3214,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>รันจากสำเนาโค้ดของ commit 24a0107 ด้วย next dev --webpack และ Chromium ตัวเต็ม เพราะมี dev server อีกตัวเปิดอยู่ในโฟลเดอร์โปรเจกต์ (Next.js ไม่ให้เปิดสองตัวในโฟลเดอร์เดียว) · CI ใช้ Turbopack และ headless shell ตามค่าปกติ</t>
+          <t>รันจากสำเนาโค้ดของ commit 24a0107 เพราะมี dev server อีกตัวเปิดอยู่ในโฟลเดอร์โปรเจกต์ (Next.js ไม่ให้เปิดสองตัวในโฟลเดอร์เดียว) · รอบที่ 1–4 ใช้ next dev --webpack · รอบที่ 5 ใช้ Turbopack ตามค่าปกติ พร้อมโค้ดที่แก้ BUG-UI-001 และ retry 2 ครั้งเหมือน CI · ใช้ Chromium ตัวเต็มของ Playwright แทน headless shell ที่ไม่ได้ติดตั้งไว้</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3833,7 @@
       </c>
       <c r="H3" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (11.72 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (8.71 วินาที)</t>
         </is>
       </c>
       <c r="I3" s="26" t="inlineStr">
@@ -3828,7 +3854,7 @@
         </is>
       </c>
       <c r="N3" s="27" t="n">
-        <v>46324.80037458333</v>
+        <v>46324.82668109953</v>
       </c>
       <c r="O3" s="28" t="inlineStr">
         <is>
@@ -3837,7 +3863,7 @@
       </c>
       <c r="P3" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/accessibility-controls.spec.ts
 ชื่อเทสต์: Owner accessibility controls › empty search results are compact, centered and clearly red</t>
         </is>
@@ -3883,7 +3909,7 @@
       </c>
       <c r="H4" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (9.49 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.72 วินาที)</t>
         </is>
       </c>
       <c r="I4" s="26" t="inlineStr">
@@ -3904,7 +3930,7 @@
         </is>
       </c>
       <c r="N4" s="27" t="n">
-        <v>46324.7917053588</v>
+        <v>46324.82678425926</v>
       </c>
       <c r="O4" s="28" t="inlineStr">
         <is>
@@ -3913,7 +3939,7 @@
       </c>
       <c r="P4" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/accessibility-controls.spec.ts
 ชื่อเทสต์: Owner accessibility controls › document toolbar exposes toggle state, keyboard navigation and focus tooltips</t>
         </is>
@@ -3959,7 +3985,7 @@
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (9.89 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.74 วินาที)</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
@@ -3980,7 +4006,7 @@
         </is>
       </c>
       <c r="N5" s="27" t="n">
-        <v>46324.791819375</v>
+        <v>46324.82682748842</v>
       </c>
       <c r="O5" s="28" t="inlineStr">
         <is>
@@ -3989,7 +4015,7 @@
       </c>
       <c r="P5" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/accessibility-controls.spec.ts
 ชื่อเทสต์: Owner accessibility controls › focus indicators are consistent for links, fields, cards and tabs</t>
         </is>
@@ -4036,7 +4062,7 @@
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.28 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.34 วินาที)</t>
         </is>
       </c>
       <c r="I6" s="26" t="inlineStr">
@@ -4057,7 +4083,7 @@
         </is>
       </c>
       <c r="N6" s="27" t="n">
-        <v>46324.79193394676</v>
+        <v>46324.82685929398</v>
       </c>
       <c r="O6" s="28" t="inlineStr">
         <is>
@@ -4066,7 +4092,7 @@
       </c>
       <c r="P6" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/accessibility-controls.spec.ts
 ชื่อเทสต์: Owner accessibility controls › dropdown supports complete keyboard navigation and type-ahead</t>
         </is>
@@ -4112,7 +4138,7 @@
       </c>
       <c r="H7" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (5.93 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.75 วินาที)</t>
         </is>
       </c>
       <c r="I7" s="26" t="inlineStr">
@@ -4133,7 +4159,7 @@
         </is>
       </c>
       <c r="N7" s="27" t="n">
-        <v>46324.79198361111</v>
+        <v>46324.82687488426</v>
       </c>
       <c r="O7" s="28" t="inlineStr">
         <is>
@@ -4142,7 +4168,7 @@
       </c>
       <c r="P7" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/accessibility-controls.spec.ts
 ชื่อเทสต์: Owner accessibility controls › keyboard menu, tooltip, contrast and mobile targets meet the UI contract</t>
         </is>
@@ -4188,7 +4214,7 @@
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (6.13 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.71 วินาที)</t>
         </is>
       </c>
       <c r="I8" s="26" t="inlineStr">
@@ -4209,7 +4235,7 @@
         </is>
       </c>
       <c r="N8" s="27" t="n">
-        <v>46324.79205238426</v>
+        <v>46324.8268952662</v>
       </c>
       <c r="O8" s="28" t="inlineStr">
         <is>
@@ -4218,7 +4244,7 @@
       </c>
       <c r="P8" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/accessibility-controls.spec.ts
 ชื่อเทสต์: Tenant accessibility controls › keyboard tooltip, contrast and mobile targets meet the UI contract</t>
         </is>
@@ -4266,7 +4292,7 @@
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.44 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (0.62 วินาที)</t>
         </is>
       </c>
       <c r="I9" s="26" t="inlineStr">
@@ -4287,7 +4313,7 @@
         </is>
       </c>
       <c r="N9" s="27" t="n">
-        <v>46324.79212358796</v>
+        <v>46324.82691521991</v>
       </c>
       <c r="O9" s="28" t="inlineStr">
         <is>
@@ -4296,7 +4322,7 @@
       </c>
       <c r="P9" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/auth-dashboard.spec.ts
 ชื่อเทสต์: rejects invalid credentials without leaking account state</t>
         </is>
@@ -4343,7 +4369,7 @@
       </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (12.39 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.91 วินาที)</t>
         </is>
       </c>
       <c r="I10" s="26" t="inlineStr">
@@ -4364,7 +4390,7 @@
         </is>
       </c>
       <c r="N10" s="27" t="n">
-        <v>46324.79216351852</v>
+        <v>46324.82692251157</v>
       </c>
       <c r="O10" s="28" t="inlineStr">
         <is>
@@ -4373,7 +4399,7 @@
       </c>
       <c r="P10" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/auth-dashboard.spec.ts
 ชื่อเทสต์: super admin can open the aggregated SaaS dashboard</t>
         </is>
@@ -4418,7 +4444,7 @@
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.97 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.92 วินาที)</t>
         </is>
       </c>
       <c r="I11" s="26" t="inlineStr">
@@ -4439,7 +4465,7 @@
         </is>
       </c>
       <c r="N11" s="27" t="n">
-        <v>46324.80051377315</v>
+        <v>46324.82696791667</v>
       </c>
       <c r="O11" s="28" t="inlineStr">
         <is>
@@ -4448,7 +4474,7 @@
       </c>
       <c r="P11" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: computed WCAG contrast › text and interactive states meet WCAG AA</t>
         </is>
@@ -4493,7 +4519,7 @@
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.65 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.39 วินาที)</t>
         </is>
       </c>
       <c r="I12" s="26" t="inlineStr">
@@ -4514,7 +4540,7 @@
         </is>
       </c>
       <c r="N12" s="27" t="n">
-        <v>46324.79244502315</v>
+        <v>46324.82700186343</v>
       </c>
       <c r="O12" s="28" t="inlineStr">
         <is>
@@ -4523,7 +4549,7 @@
       </c>
       <c r="P12" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: computed WCAG contrast › icons expose non-text contrast in default, hover and focus states</t>
         </is>
@@ -4567,7 +4593,7 @@
       </c>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.27 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.35 วินาที)</t>
         </is>
       </c>
       <c r="I13" s="26" t="inlineStr">
@@ -4588,7 +4614,7 @@
         </is>
       </c>
       <c r="N13" s="27" t="n">
-        <v>46324.79250371527</v>
+        <v>46324.82701802083</v>
       </c>
       <c r="O13" s="28" t="inlineStr">
         <is>
@@ -4597,7 +4623,7 @@
       </c>
       <c r="P13" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: computed WCAG contrast › badges meet text contrast requirements</t>
         </is>
@@ -4641,7 +4667,7 @@
       </c>
       <c r="H14" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.07 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.44 วินาที)</t>
         </is>
       </c>
       <c r="I14" s="26" t="inlineStr">
@@ -4662,7 +4688,7 @@
         </is>
       </c>
       <c r="N14" s="27" t="n">
-        <v>46324.79255331019</v>
+        <v>46324.82703373842</v>
       </c>
       <c r="O14" s="28" t="inlineStr">
         <is>
@@ -4671,7 +4697,7 @@
       </c>
       <c r="P14" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: computed WCAG contrast › input and button boundaries meet non-text contrast requirements</t>
         </is>
@@ -4715,7 +4741,7 @@
       </c>
       <c r="H15" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.35 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.58 วินาที)</t>
         </is>
       </c>
       <c r="I15" s="26" t="inlineStr">
@@ -4736,7 +4762,7 @@
         </is>
       </c>
       <c r="N15" s="27" t="n">
-        <v>46324.79260055556</v>
+        <v>46324.82705059028</v>
       </c>
       <c r="O15" s="28" t="inlineStr">
         <is>
@@ -4745,7 +4771,7 @@
       </c>
       <c r="P15" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: computed WCAG contrast › shared button variants meet text contrast in every interactive state</t>
         </is>
@@ -4789,7 +4815,7 @@
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.97 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.41 วินาที)</t>
         </is>
       </c>
       <c r="I16" s="26" t="inlineStr">
@@ -4810,7 +4836,7 @@
         </is>
       </c>
       <c r="N16" s="27" t="n">
-        <v>46324.79265099537</v>
+        <v>46324.82706895834</v>
       </c>
       <c r="O16" s="28" t="inlineStr">
         <is>
@@ -4819,7 +4845,7 @@
       </c>
       <c r="P16" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: computed WCAG contrast › semantic feedback colors meet text and boundary contrast contracts</t>
         </is>
@@ -4864,7 +4890,7 @@
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.98 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.21 วินาที)</t>
         </is>
       </c>
       <c r="I17" s="26" t="inlineStr">
@@ -4885,7 +4911,7 @@
         </is>
       </c>
       <c r="N17" s="27" t="n">
-        <v>46324.79269707176</v>
+        <v>46324.82708545139</v>
       </c>
       <c r="O17" s="28" t="inlineStr">
         <is>
@@ -4894,7 +4920,7 @@
       </c>
       <c r="P17" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: role-specific computed contrast › Tenant navigation, notification action and statuses meet WCAG AA</t>
         </is>
@@ -4939,7 +4965,7 @@
       </c>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (6.19 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.25 วินาที)</t>
         </is>
       </c>
       <c r="I18" s="26" t="inlineStr">
@@ -4960,7 +4986,7 @@
         </is>
       </c>
       <c r="N18" s="27" t="n">
-        <v>46324.79274322917</v>
+        <v>46324.82709950231</v>
       </c>
       <c r="O18" s="28" t="inlineStr">
         <is>
@@ -4969,7 +4995,7 @@
       </c>
       <c r="P18" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/contrast.spec.ts
 ชื่อเทสต์: role-specific computed contrast › Super Admin navigation and table statuses meet WCAG AA</t>
         </is>
@@ -5019,12 +5045,12 @@
       </c>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>ไม่ผ่าน: TimeoutError: locator.click: Timeout 10000ms exceeded. Call log: - waiting for getByRole('menuitem', { name: /JD-1793275969451-d6yxjh/ }) |                                                                          ^ at D:\ปี4_1\it-project\.claude\e2e-run\tests\e2e\full-billing-lifecycle.spec.ts:180:74</t>
+          <t>ผลตรงตามที่คาดหวังเมื่อรันครั้งที่ 2 (22.29 วินาที) — ครั้งแรกไม่ผ่าน (flaky) ระบบรันซ้ำอัตโนมัติแบบเดียวกับ CI</t>
         </is>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="J19" s="25" t="n"/>
@@ -5040,7 +5066,7 @@
         </is>
       </c>
       <c r="N19" s="27" t="n">
-        <v>46324.80057146991</v>
+        <v>46324.82750445602</v>
       </c>
       <c r="O19" s="28" t="inlineStr">
         <is>
@@ -5049,8 +5075,8 @@
       </c>
       <c r="P19" s="25" t="inlineStr">
         <is>
-          <t>ข้อสังเกต: ไม่ผ่านซ้ำในสภาพแวดล้อมรอบนี้ (next dev --webpack จากสำเนาโค้ด) อาการคือกดปุ่มแล้วหน้าไม่ตอบสนอง ตรงกับการกดก่อนหน้าโหลด JavaScript เสร็จ (hydration) · GitHub Actions CI run #107 บน commit 24a0107 เดียวกันผ่าน · ต้องรันซ้ำด้วย npm run test:e2e ตามปกติก่อนสรุปว่าเป็นบัค
-ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>Flaky: ครั้งแรกหมดเวลา 10 วินาทีระหว่างรอ getByRole('button', { name: 'สร้างร่างรายห้อง', exact: true }) ตอนเปิดหน้านั้นครั้งแรก (next dev คอมไพล์หน้าตอนเปิดครั้งแรก) ครั้งที่ 2 ผ่าน · ควรให้สคริปต์รอหัวข้อหน้าก่อนกดปุ่ม
+ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/full-billing-lifecycle.spec.ts
 ชื่อเทสต์: completes the critical tenant billing workflow through the owner and tenant UIs</t>
         </is>
@@ -5097,7 +5123,7 @@
       </c>
       <c r="H20" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (8.79 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.46 วินาที)</t>
         </is>
       </c>
       <c r="I20" s="26" t="inlineStr">
@@ -5118,7 +5144,7 @@
         </is>
       </c>
       <c r="N20" s="27" t="n">
-        <v>46324.80357282407</v>
+        <v>46324.82776555556</v>
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
@@ -5127,7 +5153,7 @@
       </c>
       <c r="P20" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 3 — รัน keyboard-flows ทั้งไฟล์
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/keyboard-flows.spec.ts
 ชื่อเทสต์: keyboard coverage for critical flows › Login and Owner Dashboard are operable without a pointer</t>
         </is>
@@ -5173,7 +5199,7 @@
       </c>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (5.29 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.05 วินาที)</t>
         </is>
       </c>
       <c r="I21" s="26" t="inlineStr">
@@ -5194,7 +5220,7 @@
         </is>
       </c>
       <c r="N21" s="27" t="n">
-        <v>46324.80367861111</v>
+        <v>46324.82778255787</v>
       </c>
       <c r="O21" s="28" t="inlineStr">
         <is>
@@ -5203,7 +5229,7 @@
       </c>
       <c r="P21" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 3 — รัน keyboard-flows ทั้งไฟล์
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/keyboard-flows.spec.ts
 ชื่อเทสต์: keyboard coverage for critical flows › Owner rooms, tenants and contracts support keyboard navigation</t>
         </is>
@@ -5249,7 +5275,7 @@
       </c>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.60 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.54 วินาที)</t>
         </is>
       </c>
       <c r="I22" s="26" t="inlineStr">
@@ -5270,7 +5296,7 @@
         </is>
       </c>
       <c r="N22" s="27" t="n">
-        <v>46324.80373998843</v>
+        <v>46324.82781799768</v>
       </c>
       <c r="O22" s="28" t="inlineStr">
         <is>
@@ -5279,7 +5305,7 @@
       </c>
       <c r="P22" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 3 — รัน keyboard-flows ทั้งไฟล์
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/keyboard-flows.spec.ts
 ชื่อเทสต์: keyboard coverage for critical flows › Owner invoices, meters and parcels support keyboard workflows</t>
         </is>
@@ -5325,7 +5351,7 @@
       </c>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (6.55 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.72 วินาที)</t>
         </is>
       </c>
       <c r="I23" s="26" t="inlineStr">
@@ -5346,7 +5372,7 @@
         </is>
       </c>
       <c r="N23" s="27" t="n">
-        <v>46324.80378178241</v>
+        <v>46324.82784747685</v>
       </c>
       <c r="O23" s="28" t="inlineStr">
         <is>
@@ -5355,7 +5381,7 @@
       </c>
       <c r="P23" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 3 — รัน keyboard-flows ทั้งไฟล์
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/keyboard-flows.spec.ts
 ชื่อเทสต์: keyboard coverage for critical flows › Settings, Dropdown, Action Menu and Notification Center honor keyboard contracts</t>
         </is>
@@ -5400,12 +5426,12 @@
       </c>
       <c r="H24" s="25" t="inlineStr">
         <is>
-          <t>ไม่ผ่าน: Error: expect(locator).toBeVisible() failed Locator: getByLabel('รายละเอียดบิล E2E-202607-E101', { exact: true }) Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for getByLabel('รายละเอียดบิล E2E-202607-E101', { exact: true }) |                                  ^ at D:\ปี4_1\it-project\.claude\e2e-run\tests\e2e\keyboard-f</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.68 วินาที)</t>
         </is>
       </c>
       <c r="I24" s="26" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="J24" s="25" t="n"/>
@@ -5421,7 +5447,7 @@
         </is>
       </c>
       <c r="N24" s="27" t="n">
-        <v>46324.80385769676</v>
+        <v>46324.8278790625</v>
       </c>
       <c r="O24" s="28" t="inlineStr">
         <is>
@@ -5430,8 +5456,7 @@
       </c>
       <c r="P24" s="25" t="inlineStr">
         <is>
-          <t>ข้อสังเกต: ไม่ผ่านซ้ำในสภาพแวดล้อมรอบนี้ (next dev --webpack จากสำเนาโค้ด) อาการคือกดปุ่มแล้วหน้าไม่ตอบสนอง ตรงกับการกดก่อนหน้าโหลด JavaScript เสร็จ (hydration) · GitHub Actions CI run #107 บน commit 24a0107 เดียวกันผ่าน · ต้องรันซ้ำด้วย npm run test:e2e ตามปกติก่อนสรุปว่าเป็นบัค
-ผลจากรอบที่ 3 — รัน keyboard-flows ทั้งไฟล์
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/keyboard-flows.spec.ts
 ชื่อเทสต์: keyboard coverage for critical flows › Tenant Portal navigation and modal are keyboard operable</t>
         </is>
@@ -5475,7 +5500,7 @@
       </c>
       <c r="H25" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (7.19 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.65 วินาที)</t>
         </is>
       </c>
       <c r="I25" s="26" t="inlineStr">
@@ -5496,7 +5521,7 @@
         </is>
       </c>
       <c r="N25" s="27" t="n">
-        <v>46324.80435768519</v>
+        <v>46324.82789858797</v>
       </c>
       <c r="O25" s="28" t="inlineStr">
         <is>
@@ -5505,7 +5530,7 @@
       </c>
       <c r="P25" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 4 — รันเคสที่ยังไม่ได้รัน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/keyboard-flows.spec.ts
 ชื่อเทสต์: keyboard coverage for critical flows › Super Admin navigation is covered with a seeded test account</t>
         </is>
@@ -5552,7 +5577,7 @@
       </c>
       <c r="H26" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.95 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.67 วินาที)</t>
         </is>
       </c>
       <c r="I26" s="26" t="inlineStr">
@@ -5573,7 +5598,7 @@
         </is>
       </c>
       <c r="N26" s="27" t="n">
-        <v>46324.80088405093</v>
+        <v>46324.82791795139</v>
       </c>
       <c r="O26" s="28" t="inlineStr">
         <is>
@@ -5582,7 +5607,7 @@
       </c>
       <c r="P26" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/lease-renewal.spec.ts
 ชื่อเทสต์: owner renews a lease without overwriting the active lease</t>
         </is>
@@ -5628,7 +5653,7 @@
       </c>
       <c r="H27" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (47.91 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (12.62 วินาที)</t>
         </is>
       </c>
       <c r="I27" s="26" t="inlineStr">
@@ -5649,7 +5674,7 @@
         </is>
       </c>
       <c r="N27" s="27" t="n">
-        <v>46324.80094164352</v>
+        <v>46324.8279490162</v>
       </c>
       <c r="O27" s="28" t="inlineStr">
         <is>
@@ -5658,7 +5683,7 @@
       </c>
       <c r="P27" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/mobile-touch-target.spec.ts
 ชื่อเทสต์: mobile touch target contract › 320x568 owner, tenant and super admin actions remain touch-safe</t>
         </is>
@@ -5704,7 +5729,7 @@
       </c>
       <c r="H28" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (28.52 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (10.89 วินาที)</t>
         </is>
       </c>
       <c r="I28" s="26" t="inlineStr">
@@ -5725,7 +5750,7 @@
         </is>
       </c>
       <c r="N28" s="27" t="n">
-        <v>46324.80149631944</v>
+        <v>46324.82809513889</v>
       </c>
       <c r="O28" s="28" t="inlineStr">
         <is>
@@ -5734,7 +5759,7 @@
       </c>
       <c r="P28" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/mobile-touch-target.spec.ts
 ชื่อเทสต์: mobile touch target contract › 375x667 owner, tenant and super admin actions remain touch-safe</t>
         </is>
@@ -5780,7 +5805,7 @@
       </c>
       <c r="H29" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (24.42 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (10.55 วินาที)</t>
         </is>
       </c>
       <c r="I29" s="26" t="inlineStr">
@@ -5801,7 +5826,7 @@
         </is>
       </c>
       <c r="N29" s="27" t="n">
-        <v>46324.80182658565</v>
+        <v>46324.82822133102</v>
       </c>
       <c r="O29" s="28" t="inlineStr">
         <is>
@@ -5810,7 +5835,7 @@
       </c>
       <c r="P29" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/mobile-touch-target.spec.ts
 ชื่อเทสต์: mobile touch target contract › 390x844 owner, tenant and super admin actions remain touch-safe</t>
         </is>
@@ -5856,7 +5881,7 @@
       </c>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (25.22 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (10.96 วินาที)</t>
         </is>
       </c>
       <c r="I30" s="26" t="inlineStr">
@@ -5877,7 +5902,7 @@
         </is>
       </c>
       <c r="N30" s="27" t="n">
-        <v>46324.8021093287</v>
+        <v>46324.82834349537</v>
       </c>
       <c r="O30" s="28" t="inlineStr">
         <is>
@@ -5886,7 +5911,7 @@
       </c>
       <c r="P30" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/mobile-touch-target.spec.ts
 ชื่อเทสต์: mobile touch target contract › 768x1024 owner, tenant and super admin actions remain touch-safe</t>
         </is>
@@ -5932,7 +5957,7 @@
       </c>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (21.39 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.11 วินาที)</t>
         </is>
       </c>
       <c r="I31" s="26" t="inlineStr">
@@ -5953,7 +5978,7 @@
         </is>
       </c>
       <c r="N31" s="27" t="n">
-        <v>46324.79634859954</v>
+        <v>46324.82847054398</v>
       </c>
       <c r="O31" s="28" t="inlineStr">
         <is>
@@ -5962,7 +5987,7 @@
       </c>
       <c r="P31" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/owner-dashboard-fetch.spec.ts
 ชื่อเทสต์: owner shell does not refetch the read model it already has</t>
         </is>
@@ -6008,7 +6033,7 @@
       </c>
       <c r="H32" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (24.76 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.95 วินาที)</t>
         </is>
       </c>
       <c r="I32" s="26" t="inlineStr">
@@ -6029,7 +6054,7 @@
         </is>
       </c>
       <c r="N32" s="27" t="n">
-        <v>46324.79659920139</v>
+        <v>46324.82849512732</v>
       </c>
       <c r="O32" s="28" t="inlineStr">
         <is>
@@ -6038,7 +6063,7 @@
       </c>
       <c r="P32" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/owner-dashboard-fetch.spec.ts
 ชื่อเทสต์: switching property shows the other property without refetching</t>
         </is>
@@ -6084,7 +6109,7 @@
       </c>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (9.91 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (8.70 วินาที)</t>
         </is>
       </c>
       <c r="I33" s="26" t="inlineStr">
@@ -6105,7 +6130,7 @@
         </is>
       </c>
       <c r="N33" s="27" t="n">
-        <v>46324.80240143518</v>
+        <v>46324.8285409838</v>
       </c>
       <c r="O33" s="28" t="inlineStr">
         <is>
@@ -6114,7 +6139,7 @@
       </c>
       <c r="P33" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/request-budget.spec.ts
 ชื่อเทสต์: งบคำขอของแต่ละหน้า › กางเรื่องแจ้งของผู้เช่าแล้วไม่วนโหลดซ้ำ</t>
         </is>
@@ -6160,7 +6185,7 @@
       </c>
       <c r="H34" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (21.95 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (7.62 วินาที)</t>
         </is>
       </c>
       <c r="I34" s="26" t="inlineStr">
@@ -6181,7 +6206,7 @@
         </is>
       </c>
       <c r="N34" s="27" t="n">
-        <v>46324.79725059028</v>
+        <v>46324.82864181713</v>
       </c>
       <c r="O34" s="28" t="inlineStr">
         <is>
@@ -6190,7 +6215,7 @@
       </c>
       <c r="P34" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/request-budget.spec.ts
 ชื่อเทสต์: งบคำขอของแต่ละหน้า › เปิดข้อความของเรื่องร้องเรียนฝั่งเจ้าของหอแล้วไม่วนโหลดซ้ำ</t>
         </is>
@@ -6236,7 +6261,7 @@
       </c>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (67.36 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (31.14 วินาที)</t>
         </is>
       </c>
       <c r="I35" s="26" t="inlineStr">
@@ -6257,7 +6282,7 @@
         </is>
       </c>
       <c r="N35" s="27" t="n">
-        <v>46324.79750740741</v>
+        <v>46324.82873018519</v>
       </c>
       <c r="O35" s="28" t="inlineStr">
         <is>
@@ -6266,7 +6291,7 @@
       </c>
       <c r="P35" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/request-budget.spec.ts
 ชื่อเทสต์: งบคำขอของแต่ละหน้า › ทุกหน้าหยุดยิงคำขอเมื่อโหลดเสร็จแล้ว</t>
         </is>
@@ -6312,7 +6337,7 @@
       </c>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.55 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (0.95 วินาที)</t>
         </is>
       </c>
       <c r="I36" s="26" t="inlineStr">
@@ -6333,7 +6358,7 @@
         </is>
       </c>
       <c r="N36" s="27" t="n">
-        <v>46324.79828802084</v>
+        <v>46324.82909076389</v>
       </c>
       <c r="O36" s="28" t="inlineStr">
         <is>
@@ -6342,7 +6367,7 @@
       </c>
       <c r="P36" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/responsive.spec.ts
 ชื่อเทสต์: owner workspace remains usable on a mobile viewport</t>
         </is>
@@ -6388,7 +6413,7 @@
       </c>
       <c r="H37" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.65 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.45 วินาที)</t>
         </is>
       </c>
       <c r="I37" s="26" t="inlineStr">
@@ -6409,7 +6434,7 @@
         </is>
       </c>
       <c r="N37" s="27" t="n">
-        <v>46324.79830609954</v>
+        <v>46324.82910186343</v>
       </c>
       <c r="O37" s="28" t="inlineStr">
         <is>
@@ -6418,7 +6443,7 @@
       </c>
       <c r="P37" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/responsive.spec.ts
 ชื่อเทสต์: tenant portal remains usable on a mobile viewport</t>
         </is>
@@ -6464,7 +6489,7 @@
       </c>
       <c r="H38" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.42 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (0.80 วินาที)</t>
         </is>
       </c>
       <c r="I38" s="26" t="inlineStr">
@@ -6485,7 +6510,7 @@
         </is>
       </c>
       <c r="N38" s="27" t="n">
-        <v>46324.79833701389</v>
+        <v>46324.82911876158</v>
       </c>
       <c r="O38" s="28" t="inlineStr">
         <is>
@@ -6494,7 +6519,7 @@
       </c>
       <c r="P38" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/responsive.spec.ts
 ชื่อเทสต์: super admin navigation remains usable on a mobile viewport</t>
         </is>
@@ -6539,7 +6564,7 @@
       </c>
       <c r="H39" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.87 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.56 วินาที)</t>
         </is>
       </c>
       <c r="I39" s="26" t="inlineStr">
@@ -6560,7 +6585,7 @@
         </is>
       </c>
       <c r="N39" s="27" t="n">
-        <v>46324.79835396991</v>
+        <v>46324.82912831019</v>
       </c>
       <c r="O39" s="28" t="inlineStr">
         <is>
@@ -6569,7 +6594,7 @@
       </c>
       <c r="P39" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › FULL keeps owner mutation controls available</t>
         </is>
@@ -6613,7 +6638,7 @@
       </c>
       <c r="H40" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.00 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.36 วินาที)</t>
         </is>
       </c>
       <c r="I40" s="26" t="inlineStr">
@@ -6634,7 +6659,7 @@
         </is>
       </c>
       <c r="N40" s="27" t="n">
-        <v>46324.79838729167</v>
+        <v>46324.82914642361</v>
       </c>
       <c r="O40" s="28" t="inlineStr">
         <is>
@@ -6643,7 +6668,7 @@
       </c>
       <c r="P40" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › GRACE communicates the deadline without disabling work</t>
         </is>
@@ -6688,7 +6713,7 @@
       </c>
       <c r="H41" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.96 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.25 วินาที)</t>
         </is>
       </c>
       <c r="I41" s="26" t="inlineStr">
@@ -6709,7 +6734,7 @@
         </is>
       </c>
       <c r="N41" s="27" t="n">
-        <v>46324.79841046296</v>
+        <v>46324.82916223379</v>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
@@ -6718,7 +6743,7 @@
       </c>
       <c r="P41" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › READ_ONLY preserves reading and renewal while removing mutations</t>
         </is>
@@ -6764,7 +6789,7 @@
       </c>
       <c r="H42" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (6.79 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.10 วินาที)</t>
         </is>
       </c>
       <c r="I42" s="26" t="inlineStr">
@@ -6785,7 +6810,7 @@
         </is>
       </c>
       <c r="N42" s="27" t="n">
-        <v>46324.79846799769</v>
+        <v>46324.82918833334</v>
       </c>
       <c r="O42" s="28" t="inlineStr">
         <is>
@@ -6794,7 +6819,7 @@
       </c>
       <c r="P42" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › READ_ONLY tenant can read records but cannot submit new data</t>
         </is>
@@ -6839,7 +6864,7 @@
       </c>
       <c r="H43" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.59 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.23 วินาที)</t>
         </is>
       </c>
       <c r="I43" s="26" t="inlineStr">
@@ -6860,7 +6885,7 @@
         </is>
       </c>
       <c r="N43" s="27" t="n">
-        <v>46324.79854672454</v>
+        <v>46324.82921274305</v>
       </c>
       <c r="O43" s="28" t="inlineStr">
         <is>
@@ -6869,7 +6894,7 @@
       </c>
       <c r="P43" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › responsive layouts do not overflow at mobile, tablet, or desktop widths</t>
         </is>
@@ -6915,7 +6940,7 @@
       </c>
       <c r="H44" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (5.28 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.74 วินาที)</t>
         </is>
       </c>
       <c r="I44" s="26" t="inlineStr">
@@ -6936,7 +6961,7 @@
         </is>
       </c>
       <c r="N44" s="27" t="n">
-        <v>46324.79859996528</v>
+        <v>46324.82923866898</v>
       </c>
       <c r="O44" s="28" t="inlineStr">
         <is>
@@ -6945,7 +6970,7 @@
       </c>
       <c r="P44" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › mobile actions expose at least 44 by 44 pixel touch targets</t>
         </is>
@@ -6990,7 +7015,7 @@
       </c>
       <c r="H45" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.43 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.16 วินาที)</t>
         </is>
       </c>
       <c r="I45" s="26" t="inlineStr">
@@ -7011,7 +7036,7 @@
         </is>
       </c>
       <c r="N45" s="27" t="n">
-        <v>46324.79866121527</v>
+        <v>46324.82925892361</v>
       </c>
       <c r="O45" s="28" t="inlineStr">
         <is>
@@ -7020,7 +7045,7 @@
       </c>
       <c r="P45" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › keyboard and accessibility semantics expose the read-only state</t>
         </is>
@@ -7066,7 +7091,7 @@
       </c>
       <c r="H46" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.56 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.75 วินาที)</t>
         </is>
       </c>
       <c r="I46" s="26" t="inlineStr">
@@ -7087,7 +7112,7 @@
         </is>
       </c>
       <c r="N46" s="27" t="n">
-        <v>46324.79867783565</v>
+        <v>46324.82927243056</v>
       </c>
       <c r="O46" s="28" t="inlineStr">
         <is>
@@ -7096,7 +7121,7 @@
       </c>
       <c r="P46" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › screen reader live regions announce navigation and notification count changes once</t>
         </is>
@@ -7142,7 +7167,7 @@
       </c>
       <c r="H47" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.23 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.49 วินาที)</t>
         </is>
       </c>
       <c r="I47" s="26" t="inlineStr">
@@ -7163,7 +7188,7 @@
         </is>
       </c>
       <c r="N47" s="27" t="n">
-        <v>46324.7987075</v>
+        <v>46324.82929273148</v>
       </c>
       <c r="O47" s="28" t="inlineStr">
         <is>
@@ -7172,7 +7197,7 @@
       </c>
       <c r="P47" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › shared dialog traps focus, closes on Escape, and restores trigger focus</t>
         </is>
@@ -7219,7 +7244,7 @@
       </c>
       <c r="H48" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.59 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.71 วินาที)</t>
         </is>
       </c>
       <c r="I48" s="26" t="inlineStr">
@@ -7240,7 +7265,7 @@
         </is>
       </c>
       <c r="N48" s="27" t="n">
-        <v>46324.7987333912</v>
+        <v>46324.82931005787</v>
       </c>
       <c r="O48" s="28" t="inlineStr">
         <is>
@@ -7249,7 +7274,7 @@
       </c>
       <c r="P48" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › icon tooltips support hover, focus, dismissal, action text, and mobile viewport bounds</t>
         </is>
@@ -7295,7 +7320,7 @@
       </c>
       <c r="H49" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.65 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.75 วินาที)</t>
         </is>
       </c>
       <c r="I49" s="26" t="inlineStr">
@@ -7316,7 +7341,7 @@
         </is>
       </c>
       <c r="N49" s="27" t="n">
-        <v>46324.79876354166</v>
+        <v>46324.82932993056</v>
       </c>
       <c r="O49" s="28" t="inlineStr">
         <is>
@@ -7325,7 +7350,7 @@
       </c>
       <c r="P49" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › slow access checks remain fail-closed and announce progress</t>
         </is>
@@ -7370,7 +7395,7 @@
       </c>
       <c r="H50" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.95 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.02 วินาที)</t>
         </is>
       </c>
       <c r="I50" s="26" t="inlineStr">
@@ -7391,7 +7416,7 @@
         </is>
       </c>
       <c r="N50" s="27" t="n">
-        <v>46324.79880592592</v>
+        <v>46324.82936181713</v>
       </c>
       <c r="O50" s="28" t="inlineStr">
         <is>
@@ -7400,7 +7425,7 @@
       </c>
       <c r="P50" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › network errors are not mislabeled as an expired package</t>
         </is>
@@ -7445,7 +7470,7 @@
       </c>
       <c r="H51" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.97 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (1.25 วินาที)</t>
         </is>
       </c>
       <c r="I51" s="26" t="inlineStr">
@@ -7466,7 +7491,7 @@
         </is>
       </c>
       <c r="N51" s="27" t="n">
-        <v>46324.79882859954</v>
+        <v>46324.82937368056</v>
       </c>
       <c r="O51" s="28" t="inlineStr">
         <is>
@@ -7475,7 +7500,7 @@
       </c>
       <c r="P51" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/subscription-access.spec.ts
 ชื่อเทสต์: subscription access UX › expired sessions return the user to login</t>
         </is>
@@ -7520,7 +7545,7 @@
       </c>
       <c r="H52" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (25.02 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (11.95 วินาที)</t>
         </is>
       </c>
       <c r="I52" s="26" t="inlineStr">
@@ -7541,7 +7566,7 @@
         </is>
       </c>
       <c r="N52" s="27" t="n">
-        <v>46324.79885151621</v>
+        <v>46324.82938827547</v>
       </c>
       <c r="O52" s="28" t="inlineStr">
         <is>
@@ -7550,7 +7575,7 @@
       </c>
       <c r="P52" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/table-contract.spec.ts
 ชื่อเทสต์: สัญญาของตารางทุกโรล › ตารางฝั่งเจ้าของหอครบทุกหน้า</t>
         </is>
@@ -7595,7 +7620,7 @@
       </c>
       <c r="H53" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (8.35 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.80 วินาที)</t>
         </is>
       </c>
       <c r="I53" s="26" t="inlineStr">
@@ -7616,7 +7641,7 @@
         </is>
       </c>
       <c r="N53" s="27" t="n">
-        <v>46324.79914123843</v>
+        <v>46324.82952670139</v>
       </c>
       <c r="O53" s="28" t="inlineStr">
         <is>
@@ -7625,7 +7650,7 @@
       </c>
       <c r="P53" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/table-contract.spec.ts
 ชื่อเทสต์: สัญญาของตารางทุกโรล › ตารางประวัติฝั่งผู้เช่า</t>
         </is>
@@ -7670,7 +7695,7 @@
       </c>
       <c r="H54" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (20.18 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (7.09 วินาที)</t>
         </is>
       </c>
       <c r="I54" s="26" t="inlineStr">
@@ -7691,7 +7716,7 @@
         </is>
       </c>
       <c r="N54" s="27" t="n">
-        <v>46324.79923796296</v>
+        <v>46324.82957081019</v>
       </c>
       <c r="O54" s="28" t="inlineStr">
         <is>
@@ -7700,7 +7725,7 @@
       </c>
       <c r="P54" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/table-contract.spec.ts
 ชื่อเทสต์: สัญญาของตารางทุกโรล › ตารางฝั่งผู้ดูแลระบบ</t>
         </is>
@@ -7746,7 +7771,7 @@
       </c>
       <c r="H55" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (4.06 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.17 วินาที)</t>
         </is>
       </c>
       <c r="I55" s="26" t="inlineStr">
@@ -7767,7 +7792,7 @@
         </is>
       </c>
       <c r="N55" s="27" t="n">
-        <v>46324.79947173611</v>
+        <v>46324.82965304398</v>
       </c>
       <c r="O55" s="28" t="inlineStr">
         <is>
@@ -7776,7 +7801,7 @@
       </c>
       <c r="P55" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/tenant-owner-journeys.spec.ts
 ชื่อเทสต์: owner journey › navigates room and settings tabs with the keyboard</t>
         </is>
@@ -7823,7 +7848,7 @@
       </c>
       <c r="H56" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (5.04 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.68 วินาที)</t>
         </is>
       </c>
       <c r="I56" s="26" t="inlineStr">
@@ -7844,7 +7869,7 @@
         </is>
       </c>
       <c r="N56" s="27" t="n">
-        <v>46324.79951876157</v>
+        <v>46324.82967829861</v>
       </c>
       <c r="O56" s="28" t="inlineStr">
         <is>
@@ -7853,7 +7878,7 @@
       </c>
       <c r="P56" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/tenant-owner-journeys.spec.ts
 ชื่อเทสต์: owner journey › tenant editor is accessible and protects unsaved changes</t>
         </is>
@@ -7899,7 +7924,7 @@
       </c>
       <c r="H57" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (8.70 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (3.59 วินาที)</t>
         </is>
       </c>
       <c r="I57" s="26" t="inlineStr">
@@ -7920,7 +7945,7 @@
         </is>
       </c>
       <c r="N57" s="27" t="n">
-        <v>46324.79957712963</v>
+        <v>46324.829709375</v>
       </c>
       <c r="O57" s="28" t="inlineStr">
         <is>
@@ -7929,7 +7954,7 @@
       </c>
       <c r="P57" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/tenant-owner-journeys.spec.ts
 ชื่อเทสต์: owner journey › reviews tenant onboarding and payment operations in the assigned property</t>
         </is>
@@ -7975,7 +8000,7 @@
       </c>
       <c r="H58" s="25" t="inlineStr">
         <is>
-          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (9.67 วินาที)</t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.77 วินาที)</t>
         </is>
       </c>
       <c r="I58" s="26" t="inlineStr">
@@ -7996,7 +8021,7 @@
         </is>
       </c>
       <c r="N58" s="27" t="n">
-        <v>46324.79967787037</v>
+        <v>46324.82975104167</v>
       </c>
       <c r="O58" s="28" t="inlineStr">
         <is>
@@ -8005,7 +8030,7 @@
       </c>
       <c r="P58" s="25" t="inlineStr">
         <is>
-          <t>ผลจากรอบที่ 1 — รันทั้งชุด
+          <t>ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/tenant-owner-journeys.spec.ts
 ชื่อเทสต์: tenant journey › views room, bill, PromptPay, lease, announcements and parcels</t>
         </is>
@@ -8051,16 +8076,24 @@
       </c>
       <c r="H59" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">ไม่ผ่าน: Error: expect(locator).toBeVisible() failed Locator: getByRole('dialog', { name: 'แชทกับหอพัก' }).getByText('ข้อความ E2E 1793276140216', { exact: true }) Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for getByRole('dialog', { name: 'แชทกับหอพัก' }).getByText('ข้อความ E2E 1793276140216', { exact: true }) |               </t>
+          <t>ผลตรงตามที่คาดหวัง — assertion ผ่านครบ (2.17 วินาที)</t>
         </is>
       </c>
       <c r="I59" s="26" t="inlineStr">
         <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="J59" s="25" t="n"/>
-      <c r="K59" s="25" t="n"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J59" s="25" t="inlineStr">
+        <is>
+          <t>BUG-UI-001</t>
+        </is>
+      </c>
+      <c r="K59" s="25" t="inlineStr">
+        <is>
+          <t>Medium / P2</t>
+        </is>
+      </c>
       <c r="L59" s="25" t="inlineStr">
         <is>
           <t>DEV (127.0.0.1:3317 · next dev) · Chromium (Playwright 1.62) headless · 1280×720 · PostgreSQL 17.10 (nestly_test) · Windows 11</t>
@@ -8072,7 +8105,7 @@
         </is>
       </c>
       <c r="N59" s="27" t="n">
-        <v>46324.80251629629</v>
+        <v>46324.82978326389</v>
       </c>
       <c r="O59" s="28" t="inlineStr">
         <is>
@@ -8081,8 +8114,8 @@
       </c>
       <c r="P59" s="25" t="inlineStr">
         <is>
-          <t>ข้อสังเกต: ไม่ผ่านซ้ำในสภาพแวดล้อมรอบนี้ (next dev --webpack จากสำเนาโค้ด) อาการคือกดปุ่มแล้วหน้าไม่ตอบสนอง ตรงกับการกดก่อนหน้าโหลด JavaScript เสร็จ (hydration) · GitHub Actions CI run #107 บน commit 24a0107 เดียวกันผ่าน · ต้องรันซ้ำด้วย npm run test:e2e ตามปกติก่อนสรุปว่าเป็นบัค
-ผลจากรอบที่ 2 — รันซ้ำเฉพาะเคสที่ไม่ผ่าน
+          <t>เคสนี้พบ BUG-UI-001 (ส่งแชทก่อนโหลดบทสนทนาเสร็จแล้วเงียบ) แก้แล้วและทดสอบซ้ำผ่าน
+ผลจากรอบที่ 5 — หลังแก้ BUG-UI-001 รันทั้งชุด (Turbopack, retry 2 ครั้งแบบ CI)
 สคริปต์: tests/e2e/tenant-owner-journeys.spec.ts
 ชื่อเทสต์: tenant journey › creates a repair ticket and sends a chat message</t>
         </is>
@@ -8187,7 +8220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8303,185 +8336,92 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="30" t="n"/>
+    <row r="3" ht="190" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>BUG-UI-001</t>
+        </is>
+      </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>TC_UI_BILL_001</t>
+          <t>TC_UI_TENANT_002</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>รอบบิลครบวงจรผ่านหน้าจอจริง ตั้งแต่สมัครเจ้าของหอจนรับชำระเงิน</t>
-        </is>
-      </c>
-      <c r="D3" s="30" t="n"/>
-      <c r="E3" s="30" t="n"/>
+          <t>ผู้เช่ากดส่งแชทก่อนโหลดบทสนทนาเสร็จ ข้อความไม่ถูกส่งและไม่มีแจ้งเตือน</t>
+        </is>
+      </c>
+      <c r="D3" s="25" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
       <c r="F3" s="25" t="inlineStr">
         <is>
-          <t>1. สร้างเจ้าของหอใหม่ (PENDING) → Super Admin อนุมัติ
-2. เจ้าของหอตั้งรหัสใหม่ → ยอมรับนโยบาย → สลับหอ
-3. สร้างคำเชิญ → ผู้เช่าสมัครที่ /register
-4. เจ้าของหออนุมัติคำขอเข้าพัก → สร้างสัญญา (มัดจำ 7,000)
-5. จดมิเตอร์น้ำและไฟ → สร้างร่างบิล → ออกบิล
-6. ผู้เช่าเปิดบิล เห็น QR PromptPay → ส่งสลิป PNG
-7. เจ้าของหอตรวจและยืนยันรับชำระ</t>
+          <t>1. เข้าสู่ระบบด้วยบัญชีผู้เช่า
+2. กดปุ่มเปิดแชทกับหอพัก
+3. พิมพ์ข้อความแล้วกดส่งทันที ก่อนรายการข้อความโหลดเสร็จ</t>
         </is>
       </c>
       <c r="G3" s="25" t="inlineStr">
         <is>
-          <t>สมัครผู้เช่าได้ 201 "สมัครสำเร็จ" · สัญญาเป็นฉบับร่าง · มิเตอร์ "บันทึกแล้ว" · บิลยอด &gt; 3,500 สถานะ "รอชำระ" · สลิป "รอตรวจสอบ" ยอดตรงบิล · ยืนยันแล้วบิลเป็นชำระแล้ว</t>
+          <t>ส่งข้อความได้ หรือปุ่มส่งยังกดไม่ได้จนกว่าแชทพร้อม</t>
         </is>
       </c>
       <c r="H3" s="25" t="inlineStr">
         <is>
-          <t>ไม่ผ่าน: TimeoutError: locator.click: Timeout 10000ms exceeded. Call log: - waiting for getByRole('menuitem', { name: /JD-1793275969451-d6yxjh/ }) |                                                                          ^ at D:\ปี4_1\it-project\.claude\e2e-run\tests\e2e\full-billing-lifecycle.spec.ts:180:74</t>
+          <t>ไม่มีคำขอ POST /api/v1/tenant/chat ออกไป ข้อความค้างในช่องพิมพ์ และไม่มีข้อความแจ้งเตือน (ตรวจจาก Playwright trace)</t>
         </is>
       </c>
       <c r="I3" s="25" t="inlineStr">
         <is>
-          <t>ข้อสังเกต: ไม่ผ่านซ้ำในสภาพแวดล้อมรอบนี้ (next dev --webpack จากสำเนาโค้ด) อาการคือกดปุ่มแล้วหน้าไม่ตอบสนอง ตรงกับการกดก่อนหน้าโหลด JavaScript เสร็จ (hydration) · GitHub Actions CI run #107 บน commit 24a0107 เดียวกันผ่าน · ต้องรันซ้ำด้วย npm run test:e2e ตามปกติก่อนสรุปว่าเป็นบัค</t>
-        </is>
-      </c>
-      <c r="J3" s="30" t="n"/>
+          <t>ผู้ใช้เข้าใจว่าส่งแล้ว แต่หอพักไม่ได้รับข้อความ เกิดบ่อยเมื่อเน็ตหรือเครื่องช้า และเกิดได้กับแชทของเจ้าของหอและ Super Admin ด้วย</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="inlineStr">
+        <is>
+          <t>ปิดปุ่มส่งและปุ่มแนบไฟล์จนกว่าโหลดบทสนทนาเสร็จ และให้สตรีมล้างเฉพาะข้อความเตือนเรื่องการเชื่อมต่อ ไม่ล้าง error อื่น</t>
+        </is>
+      </c>
       <c r="K3" s="25" t="inlineStr">
         <is>
-          <t>tests/e2e/full-billing-lifecycle.spec.ts</t>
+          <t>components/chat/use-chat-thread.ts · components/chat/ChatParts.tsx · components/tenant/TenantPortal.tsx · components/dorm/ChatWidget.tsx · components/admin/SuperAdminChatWidget.tsx</t>
         </is>
       </c>
       <c r="L3" s="25" t="inlineStr">
         <is>
-          <t>evidence-ui/TC_UI_BILL_001.png</t>
-        </is>
-      </c>
-      <c r="M3" s="31" t="n">
-        <v>46324.80057146991</v>
+          <t>Playwright trace ของรอบที่ 2–4: กดส่งแล้วไม่มีคำขอ POST</t>
+        </is>
+      </c>
+      <c r="M3" s="30" t="n">
+        <v>46324.81944444445</v>
       </c>
       <c r="N3" s="25" t="inlineStr">
         <is>
-          <t>รอยืนยัน — ยังไม่ออก Defect ID</t>
-        </is>
-      </c>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="30" t="n"/>
-      <c r="B4" s="25" t="inlineStr">
-        <is>
-          <t>TC_UI_KEY_005</t>
-        </is>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>เมนูและ modal ฝั่งผู้เช่าใช้คีย์บอร์ดได้</t>
-        </is>
-      </c>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="25" t="inlineStr">
-        <is>
-          <t>1. ใช้ Tab ไปตามเมนูผู้เช่า
-2. เปิด modal ด้วย Enter แล้วปิดด้วย Escape</t>
-        </is>
-      </c>
-      <c r="G4" s="25" t="inlineStr">
-        <is>
-          <t>เปิดทุกเมนูได้ · modal กัก focus และคืน focus หลังปิด</t>
-        </is>
-      </c>
-      <c r="H4" s="25" t="inlineStr">
-        <is>
-          <t>ไม่ผ่าน: Error: expect(locator).toBeVisible() failed Locator: getByLabel('รายละเอียดบิล E2E-202607-E101', { exact: true }) Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for getByLabel('รายละเอียดบิล E2E-202607-E101', { exact: true }) |                                  ^ at D:\ปี4_1\it-project\.claude\e2e-run\tests\e2e\keyboard-f</t>
-        </is>
-      </c>
-      <c r="I4" s="25" t="inlineStr">
-        <is>
-          <t>ข้อสังเกต: ไม่ผ่านซ้ำในสภาพแวดล้อมรอบนี้ (next dev --webpack จากสำเนาโค้ด) อาการคือกดปุ่มแล้วหน้าไม่ตอบสนอง ตรงกับการกดก่อนหน้าโหลด JavaScript เสร็จ (hydration) · GitHub Actions CI run #107 บน commit 24a0107 เดียวกันผ่าน · ต้องรันซ้ำด้วย npm run test:e2e ตามปกติก่อนสรุปว่าเป็นบัค</t>
-        </is>
-      </c>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="25" t="inlineStr">
-        <is>
-          <t>tests/e2e/keyboard-flows.spec.ts</t>
-        </is>
-      </c>
-      <c r="L4" s="25" t="inlineStr">
-        <is>
-          <t>evidence-ui/TC_UI_KEY_005.png</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="n">
-        <v>46324.80385769676</v>
-      </c>
-      <c r="N4" s="25" t="inlineStr">
-        <is>
-          <t>รอยืนยัน — ยังไม่ออก Defect ID</t>
-        </is>
-      </c>
-      <c r="O4" s="25" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="25" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="30" t="n"/>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>TC_UI_TENANT_002</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>ผู้เช่าแจ้งซ่อมและส่งข้อความแชทถึงหอพัก</t>
-        </is>
-      </c>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t>1. เมนูแจ้งเรื่อง → กดแจ้งเรื่อง
-2. กรอกหัวข้อ รายละเอียด เลือกความเร่งด่วน "ด่วน" → ส่งเรื่อง
-3. กดเปิดแชทกับหอพัก → พิมพ์ข้อความ → ส่งข้อความ</t>
-        </is>
-      </c>
-      <c r="G5" s="25" t="inlineStr">
-        <is>
-          <t>เรื่อง "ก๊อกน้ำ E2E รั่ว" ปรากฏพร้อมป้าย "ด่วน" · ข้อความแชทแสดงในหน้าต่างแชท</t>
-        </is>
-      </c>
-      <c r="H5" s="25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ไม่ผ่าน: Error: expect(locator).toBeVisible() failed Locator: getByRole('dialog', { name: 'แชทกับหอพัก' }).getByText('ข้อความ E2E 1793276140216', { exact: true }) Expected: visible Timeout: 5000ms Error: element(s) not found Call log: - Expect "toBeVisible" with timeout 5000ms - waiting for getByRole('dialog', { name: 'แชทกับหอพัก' }).getByText('ข้อความ E2E 1793276140216', { exact: true }) |               </t>
-        </is>
-      </c>
-      <c r="I5" s="25" t="inlineStr">
-        <is>
-          <t>ข้อสังเกต: ไม่ผ่านซ้ำในสภาพแวดล้อมรอบนี้ (next dev --webpack จากสำเนาโค้ด) อาการคือกดปุ่มแล้วหน้าไม่ตอบสนอง ตรงกับการกดก่อนหน้าโหลด JavaScript เสร็จ (hydration) · GitHub Actions CI run #107 บน commit 24a0107 เดียวกันผ่าน · ต้องรันซ้ำด้วย npm run test:e2e ตามปกติก่อนสรุปว่าเป็นบัค</t>
-        </is>
-      </c>
-      <c r="J5" s="30" t="n"/>
-      <c r="K5" s="25" t="inlineStr">
-        <is>
-          <t>tests/e2e/tenant-owner-journeys.spec.ts</t>
-        </is>
-      </c>
-      <c r="L5" s="25" t="inlineStr">
+          <t>Fixed (รอ merge)</t>
+        </is>
+      </c>
+      <c r="O3" s="25" t="inlineStr">
+        <is>
+          <t>useChatThread คืนค่า isReady (โหลดเสร็จและมี conversationId) ช่องพิมพ์ทั้ง 3 จุดปิดปุ่มส่ง/แนบไฟล์เมื่อ isReady เป็น false · stream.onopen ล้างเฉพาะข้อความเตือนการเชื่อมต่อ</t>
+        </is>
+      </c>
+      <c r="P3" s="25" t="inlineStr">
+        <is>
+          <t>Pass (TC_UI_TENANT_002 ในรอบที่ 5)</t>
+        </is>
+      </c>
+      <c r="Q3" s="25" t="inlineStr">
         <is>
           <t>evidence-ui/TC_UI_TENANT_002.png</t>
         </is>
       </c>
-      <c r="M5" s="31" t="n">
-        <v>46324.80251629629</v>
-      </c>
-      <c r="N5" s="25" t="inlineStr">
-        <is>
-          <t>รอยืนยัน — ยังไม่ออก Defect ID</t>
-        </is>
-      </c>
-      <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
